--- a/docs/ЗАДАНИЯ 1.15.0 — по семействам.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — по семействам.xlsx
@@ -1875,12 +1875,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД перенеси два своих здания на другие гексы</t>
+          <t>В ЭТОТ ХОД снеси своё здание и построй другое</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Одно из перенесённых - твоё ЦУ</t>
+          <t>Построенное встало на тот же гекс, где стояло снесённое</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>переносу зданий атака не нужна; зато она нужна тому, кому переносить уже нечего</t>
+          <t>перестройке атака не нужна; зато она нужна тому, кому перестраивать уже нечего</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>низ копит чужие обломки, верх защищает свои здания: одна война, но разные её концы</t>
+          <t>низ копит чужие трофеи, верх защищает свои здания: одна война, но разные её концы</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ЭВАКУАЦИЯ ОБЛОМКОВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
+          <t>ЭВАКУАЦИЯ ТРОФЕЕВ: твой уничтоженный жетон уходит в твой запас, а не на место уничтоженных жетонов атаковавшего</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">

--- a/docs/ЗАДАНИЯ 1.15.0 — по семействам.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — по семействам.xlsx
@@ -1533,12 +1533,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД воспользуйся тремя разными предложениями Науки</t>
+          <t>В ЭТОТ ХОД сдай трофеи на ДВУХ разных треках технологий</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>На трёх треках</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>пара к карте 13: то же требование и почти та же цена, но платят разным — там смесь с картой задания, здесь чистые монеты</t>
+          <t>два трека за ход — это два шага, оплаченных трофеями; атака сверху их не заменит — но пригодится тому, кому сдавать нечего</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД построй или перенеси своё ЦУ так, чтобы от него до гекса с ЦУ противника осталось не больше 2 гексов</t>
+          <t>В ЭТОТ ХОД поставь своё ЦУ так, чтобы от него до гекса с ЦУ противника осталось не больше 2 гексов</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>перенос ЦУ — это стройка, а не смена энергии: верх не подменяет низ, но выручает, когда ЦУ уехало и всё осталось без питания</t>
+          <t>постановка ЦУ — это стройка, а не смена энергии: верх не подменяет низ, но выручает, когда ЦУ уехало и всё осталось без питания</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2835,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Имей среди уничтоженных жетонов жетон врага</t>
+          <t>Имей среди уничтоженных жетонов жетоны ДВУХ разных противников</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>два жетона, оба ценностью 2 и выше</t>
+          <t>И оба этих жетона — здания</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>

--- a/docs/ЗАДАНИЯ 1.15.0 — по семействам.xlsx
+++ b/docs/ЗАДАНИЯ 1.15.0 — по семействам.xlsx
@@ -1708,17 +1708,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД</t>
+          <t>СОСТОЯНИЕ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД поставь своё ЦУ так, чтобы от него до гекса с ЦУ противника осталось не больше 2 гексов</t>
+          <t>Имей своё здание на гексе, соседнем с гексом, где стоит ЦУ противника</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>В ЭТОТ ХОД поставь его так, чтобы оно примыкало к зданию противника</t>
+          <t>Твоих зданий вокруг чужого ЦУ два, и стоят они на разных гексах</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>постановка ЦУ — это стройка, а не смена энергии: верх не подменяет низ, но выручает, когда ЦУ уехало и всё осталось без питания</t>
+          <t>подобраться зданием к чужому штабу — это стройка, а смена энергии её не заменит; зато выручит того, у кого стройка уже встала без питания</t>
         </is>
       </c>
     </row>
@@ -4143,14 +4143,14 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1, 3, 6, 7, 8, 9, 10, 12, 17, 21, 29, 30, 31, 36, 37, 39, 40</t>
+          <t>1, 3, 6, 7, 8, 9, 10, 12, 15, 17, 21, 29, 30, 31, 36, 37, 39, 40</t>
         </is>
       </c>
     </row>
@@ -4166,14 +4166,14 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2, 4, 5, 11, 13, 14, 15, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 32, 33, 34, 35, 38</t>
+          <t>2, 4, 5, 11, 13, 14, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 32, 33, 34, 35, 38</t>
         </is>
       </c>
     </row>
